--- a/sample_data/A_arabic_pharmacy_report.xlsx
+++ b/sample_data/A_arabic_pharmacy_report.xlsx
@@ -505,22 +505,22 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="F5" t="n">
-        <v>2286.34</v>
+        <v>2639.25</v>
       </c>
       <c r="G5" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="H5" t="n">
         <v>38.25</v>
       </c>
       <c r="I5" t="n">
-        <v>46.66</v>
+        <v>35.19</v>
       </c>
       <c r="J5" s="1" t="n">
-        <v>46641</v>
+        <v>46567</v>
       </c>
     </row>
     <row r="6">
@@ -543,22 +543,22 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>172</v>
+        <v>79</v>
       </c>
       <c r="F6" t="n">
-        <v>7217.12</v>
+        <v>3424.65</v>
       </c>
       <c r="G6" t="n">
-        <v>112</v>
+        <v>4</v>
       </c>
       <c r="H6" t="n">
-        <v>34.39</v>
+        <v>35.53</v>
       </c>
       <c r="I6" t="n">
-        <v>41.96</v>
+        <v>43.35</v>
       </c>
       <c r="J6" s="1" t="n">
-        <v>46337</v>
+        <v>47081</v>
       </c>
     </row>
     <row r="7">
@@ -587,16 +587,16 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="H7" t="n">
-        <v>41.29</v>
+        <v>41.46</v>
       </c>
       <c r="I7" t="n">
-        <v>49.55</v>
+        <v>49.75</v>
       </c>
       <c r="J7" s="1" t="n">
-        <v>46689</v>
+        <v>46849</v>
       </c>
     </row>
     <row r="8">
@@ -619,23 +619,23 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="F8" t="n">
-        <v>1397.94</v>
+        <v>446.32</v>
       </c>
       <c r="G8" t="n">
-        <v>54</v>
+        <v>7</v>
       </c>
       <c r="H8" t="n">
-        <v>51.51</v>
+        <v>54.03</v>
       </c>
       <c r="I8" t="n">
-        <v>60.78</v>
+        <v>63.76</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>12/2028</t>
+          <t>09/2027</t>
         </is>
       </c>
     </row>
@@ -662,20 +662,20 @@
         <v>70</v>
       </c>
       <c r="F9" t="n">
-        <v>2373.7</v>
+        <v>2508.8</v>
       </c>
       <c r="G9" t="n">
-        <v>13</v>
+        <v>49</v>
       </c>
       <c r="H9" t="n">
-        <v>27.13</v>
+        <v>28.67</v>
       </c>
       <c r="I9" t="n">
-        <v>33.91</v>
+        <v>35.84</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>13-09-2028</t>
+          <t>28-10-2028</t>
         </is>
       </c>
     </row>
@@ -707,16 +707,16 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="H10" t="n">
-        <v>32.09</v>
+        <v>31.43</v>
       </c>
       <c r="I10" t="n">
-        <v>29.52</v>
+        <v>38.03</v>
       </c>
       <c r="J10" s="1" t="n">
-        <v>47089</v>
+        <v>46925</v>
       </c>
     </row>
     <row r="11">
@@ -739,24 +739,24 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>162</v>
+        <v>113</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>21,456.90 ج.م</t>
+          <t>15,850.51 ج.م</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H11" t="n">
-        <v>115.17</v>
+        <v>121.97</v>
       </c>
       <c r="I11" t="n">
-        <v>132.45</v>
+        <v>140.27</v>
       </c>
       <c r="J11" s="1" t="n">
-        <v>47207</v>
+        <v>46677</v>
       </c>
     </row>
     <row r="12">
@@ -779,23 +779,23 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>129</v>
+        <v>96</v>
       </c>
       <c r="F12" t="n">
-        <v>13710.12</v>
+        <v>10040.64</v>
       </c>
       <c r="G12" t="n">
-        <v>20</v>
+        <v>56</v>
       </c>
       <c r="H12" t="n">
-        <v>92.42</v>
+        <v>90.95</v>
       </c>
       <c r="I12" t="n">
-        <v>106.28</v>
+        <v>104.59</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>08/2027</t>
+          <t>08/2028</t>
         </is>
       </c>
     </row>
@@ -825,18 +825,18 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H13" t="n">
-        <v>109.71</v>
+        <v>101.53</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>128.36 جنيه</t>
+          <t>118.79 جنيه</t>
         </is>
       </c>
       <c r="J13" s="1" t="n">
-        <v>47106</v>
+        <v>46767</v>
       </c>
     </row>
     <row r="14">
@@ -865,17 +865,17 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="H14" t="n">
-        <v>24.52</v>
+        <v>23.51</v>
       </c>
       <c r="I14" t="n">
-        <v>30.65</v>
+        <v>29.39</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>11-10-2026</t>
+          <t>22-03-2028</t>
         </is>
       </c>
     </row>
@@ -899,22 +899,22 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="F15" t="n">
-        <v>2201.76</v>
+        <v>5035.06</v>
       </c>
       <c r="G15" t="n">
-        <v>6</v>
+        <v>190</v>
       </c>
       <c r="H15" t="n">
-        <v>79.09</v>
+        <v>73.56999999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>91.73999999999999</v>
+        <v>85.34</v>
       </c>
       <c r="J15" s="1" t="n">
-        <v>47082</v>
+        <v>46371</v>
       </c>
     </row>
     <row r="16">
@@ -938,24 +938,24 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>٤</t>
+          <t>١</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>788.52</v>
+        <v>183.86</v>
       </c>
       <c r="G16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H16" t="n">
-        <v>172.92</v>
+        <v>161.28</v>
       </c>
       <c r="I16" t="n">
-        <v>197.13</v>
+        <v>183.86</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>12/2028</t>
+          <t>04/2028</t>
         </is>
       </c>
     </row>
@@ -979,22 +979,22 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>438</v>
+        <v>150</v>
       </c>
       <c r="F17" t="n">
-        <v>44216.1</v>
+        <v>14658</v>
       </c>
       <c r="G17" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="H17" t="n">
-        <v>87.03</v>
+        <v>84.23999999999999</v>
       </c>
       <c r="I17" t="n">
-        <v>100.95</v>
+        <v>97.72</v>
       </c>
       <c r="J17" s="1" t="n">
-        <v>46969</v>
+        <v>46548</v>
       </c>
     </row>
     <row r="18">
@@ -1017,24 +1017,24 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>794.64 ج.م</t>
+          <t>1,220.77 ج.م</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="H18" t="n">
-        <v>61.22</v>
+        <v>60.86</v>
       </c>
       <c r="I18" t="n">
-        <v>72.23999999999999</v>
+        <v>71.81</v>
       </c>
       <c r="J18" s="1" t="n">
-        <v>47023</v>
+        <v>46849</v>
       </c>
     </row>
     <row r="19">
@@ -1057,23 +1057,23 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>154</v>
+        <v>60</v>
       </c>
       <c r="F19" t="n">
-        <v>13679.82</v>
+        <v>5720.4</v>
       </c>
       <c r="G19" t="n">
-        <v>476</v>
+        <v>32</v>
       </c>
       <c r="H19" t="n">
-        <v>75.28</v>
+        <v>80.8</v>
       </c>
       <c r="I19" t="n">
-        <v>88.83</v>
+        <v>95.34</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>18-03-2028</t>
+          <t>29-11-2026</t>
         </is>
       </c>
     </row>
@@ -1097,19 +1097,19 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>168</v>
+        <v>142</v>
       </c>
       <c r="F20" t="n">
-        <v>18291.84</v>
+        <v>15353.04</v>
       </c>
       <c r="G20" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="H20" t="n">
-        <v>93.86</v>
+        <v>93.20999999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>108.88</v>
+        <v>108.12</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -1137,22 +1137,22 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="F21" t="n">
-        <v>14509.52</v>
+        <v>17044.83</v>
       </c>
       <c r="G21" t="n">
-        <v>185</v>
+        <v>5</v>
       </c>
       <c r="H21" t="n">
-        <v>191.65</v>
+        <v>186.22</v>
       </c>
       <c r="I21" t="n">
-        <v>216.56</v>
+        <v>210.43</v>
       </c>
       <c r="J21" s="1" t="n">
-        <v>47186</v>
+        <v>47219</v>
       </c>
     </row>
     <row r="22">
@@ -1176,25 +1176,25 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>٧</t>
+          <t>٦</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1617</v>
+        <v>1411.74</v>
       </c>
       <c r="G22" t="n">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="H22" t="n">
-        <v>206.25</v>
+        <v>210.08</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>231.0 جنيه</t>
+          <t>235.29 جنيه</t>
         </is>
       </c>
       <c r="J22" s="1" t="n">
-        <v>46297</v>
+        <v>46982</v>
       </c>
     </row>
     <row r="23">
@@ -1223,16 +1223,16 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H23" t="n">
-        <v>9.34</v>
+        <v>9.43</v>
       </c>
       <c r="I23" t="n">
-        <v>12.14</v>
+        <v>12.26</v>
       </c>
       <c r="J23" s="1" t="n">
-        <v>46825</v>
+        <v>46706</v>
       </c>
     </row>
     <row r="24">
@@ -1255,19 +1255,19 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>164</v>
+        <v>43</v>
       </c>
       <c r="F24" t="n">
-        <v>45172.16</v>
+        <v>11944.54</v>
       </c>
       <c r="G24" t="n">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="H24" t="n">
-        <v>248.14</v>
+        <v>250.25</v>
       </c>
       <c r="I24" t="n">
-        <v>275.44</v>
+        <v>277.78</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -1295,24 +1295,24 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>4,252.50 ج.م</t>
+          <t>5,037.30 ج.م</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H25" t="n">
-        <v>43.75</v>
+        <v>46.64</v>
       </c>
       <c r="I25" t="n">
-        <v>52.5</v>
+        <v>55.97</v>
       </c>
       <c r="J25" s="1" t="n">
-        <v>46342</v>
+        <v>46542</v>
       </c>
     </row>
     <row r="26">
@@ -1335,22 +1335,19 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>528</v>
+        <v>122</v>
       </c>
       <c r="F26" t="n">
-        <v>35682.24</v>
+        <v>8350.9</v>
       </c>
       <c r="G26" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>56.79</v>
+        <v>57.52</v>
       </c>
       <c r="I26" t="n">
-        <v>67.58</v>
-      </c>
-      <c r="J26" s="1" t="n">
-        <v>46532</v>
+        <v>68.45</v>
       </c>
     </row>
     <row r="27">
@@ -1373,22 +1370,22 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>173</v>
+        <v>49</v>
       </c>
       <c r="F27" t="n">
-        <v>14059.71</v>
+        <v>4114.53</v>
       </c>
       <c r="G27" t="n">
-        <v>56</v>
+        <v>23</v>
       </c>
       <c r="H27" t="n">
-        <v>68.87</v>
+        <v>71.16</v>
       </c>
       <c r="I27" t="n">
-        <v>81.27</v>
+        <v>83.97</v>
       </c>
       <c r="J27" s="1" t="n">
-        <v>47142</v>
+        <v>47047</v>
       </c>
     </row>
     <row r="28">
@@ -1412,24 +1409,24 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>٣٢٠</t>
+          <t>٣٠٠</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>140204.8</v>
+        <v>129201</v>
       </c>
       <c r="G28" t="n">
-        <v>74</v>
+        <v>10</v>
       </c>
       <c r="H28" t="n">
-        <v>398.31</v>
+        <v>391.52</v>
       </c>
       <c r="I28" t="n">
-        <v>438.14</v>
+        <v>430.67</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>10/2028</t>
+          <t>04/2028</t>
         </is>
       </c>
     </row>
@@ -1453,23 +1450,23 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F29" t="n">
-        <v>6077.16</v>
+        <v>5629.89</v>
       </c>
       <c r="G29" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="H29" t="n">
-        <v>304.16</v>
+        <v>298.35</v>
       </c>
       <c r="I29" t="n">
-        <v>337.62</v>
+        <v>331.17</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>14-01-2029</t>
+          <t>23-01-2029</t>
         </is>
       </c>
     </row>
@@ -1493,19 +1490,22 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>355</v>
+        <v>401</v>
       </c>
       <c r="F30" t="n">
-        <v>193911.65</v>
+        <v>228321.38</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>109</v>
       </c>
       <c r="H30" t="n">
-        <v>505.77</v>
+        <v>527.2</v>
       </c>
       <c r="I30" t="n">
-        <v>546.23</v>
+        <v>569.38</v>
+      </c>
+      <c r="J30" s="1" t="n">
+        <v>46796</v>
       </c>
     </row>
     <row r="31">
@@ -1528,24 +1528,24 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>159</v>
+        <v>83</v>
       </c>
       <c r="F31" t="n">
-        <v>28794.9</v>
+        <v>15815.65</v>
       </c>
       <c r="G31" t="n">
-        <v>29</v>
+        <v>62</v>
       </c>
       <c r="H31" t="n">
-        <v>164.64</v>
+        <v>173.23</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>181.1 جنيه</t>
+          <t>190.55 جنيه</t>
         </is>
       </c>
       <c r="J31" s="1" t="n">
-        <v>46646</v>
+        <v>46965</v>
       </c>
     </row>
     <row r="32">
@@ -1568,25 +1568,25 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>3,802.36 ج.م</t>
+          <t>332.94 ج.م</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>110</v>
+        <v>14</v>
       </c>
       <c r="H32" t="n">
-        <v>142.52</v>
+        <v>143.51</v>
       </c>
       <c r="I32" t="n">
-        <v>165.32</v>
+        <v>166.47</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>09/2027</t>
+          <t>05/2028</t>
         </is>
       </c>
     </row>
@@ -1610,22 +1610,22 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>167</v>
+        <v>57</v>
       </c>
       <c r="F33" t="n">
-        <v>21846.94</v>
+        <v>7785.63</v>
       </c>
       <c r="G33" t="n">
-        <v>431</v>
+        <v>183</v>
       </c>
       <c r="H33" t="n">
-        <v>111.81</v>
+        <v>116.74</v>
       </c>
       <c r="I33" t="n">
-        <v>130.82</v>
+        <v>136.59</v>
       </c>
       <c r="J33" s="1" t="n">
-        <v>47059</v>
+        <v>46997</v>
       </c>
     </row>
     <row r="34">
@@ -1649,24 +1649,24 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>١٥</t>
+          <t>٣١</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>597.45</v>
+        <v>1191.02</v>
       </c>
       <c r="G34" t="n">
-        <v>20</v>
+        <v>106</v>
       </c>
       <c r="H34" t="n">
-        <v>32.12</v>
+        <v>30.98</v>
       </c>
       <c r="I34" t="n">
-        <v>39.83</v>
+        <v>38.42</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>18-08-2027</t>
+          <t>20-03-2028</t>
         </is>
       </c>
     </row>
@@ -1690,22 +1690,22 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>125</v>
+        <v>60</v>
       </c>
       <c r="F35" t="n">
-        <v>5662.5</v>
+        <v>2814.6</v>
       </c>
       <c r="G35" t="n">
-        <v>398</v>
+        <v>12</v>
       </c>
       <c r="H35" t="n">
-        <v>37.13</v>
+        <v>38.45</v>
       </c>
       <c r="I35" t="n">
-        <v>45.3</v>
+        <v>46.91</v>
       </c>
       <c r="J35" s="1" t="n">
-        <v>46989</v>
+        <v>47008</v>
       </c>
     </row>
     <row r="36">
@@ -1728,23 +1728,23 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="F36" t="n">
-        <v>14374.6</v>
+        <v>13382.08</v>
       </c>
       <c r="G36" t="n">
-        <v>10</v>
+        <v>467</v>
       </c>
       <c r="H36" t="n">
-        <v>73.04000000000001</v>
+        <v>73.37</v>
       </c>
       <c r="I36" t="n">
-        <v>87.65000000000001</v>
+        <v>88.04000000000001</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>12/2026</t>
+          <t>12/2028</t>
         </is>
       </c>
     </row>
@@ -1768,22 +1768,22 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>141</v>
+        <v>170</v>
       </c>
       <c r="F37" t="n">
-        <v>6232.2</v>
+        <v>7420.5</v>
       </c>
       <c r="G37" t="n">
-        <v>7</v>
+        <v>107</v>
       </c>
       <c r="H37" t="n">
-        <v>36.23</v>
+        <v>35.78</v>
       </c>
       <c r="I37" t="n">
-        <v>44.2</v>
+        <v>43.65</v>
       </c>
       <c r="J37" s="1" t="n">
-        <v>46649</v>
+        <v>46875</v>
       </c>
     </row>
     <row r="38">
@@ -1806,22 +1806,22 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="F38" t="n">
-        <v>1661.76</v>
+        <v>725.2</v>
       </c>
       <c r="G38" t="n">
-        <v>59</v>
+        <v>23</v>
       </c>
       <c r="H38" t="n">
-        <v>42.92</v>
+        <v>42.81</v>
       </c>
       <c r="I38" t="n">
-        <v>51.93</v>
+        <v>51.8</v>
       </c>
       <c r="J38" s="1" t="n">
-        <v>46987</v>
+        <v>46929</v>
       </c>
     </row>
     <row r="39">
@@ -1852,17 +1852,17 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="H39" t="n">
-        <v>48.62</v>
+        <v>49.05</v>
       </c>
       <c r="I39" t="n">
-        <v>58.83</v>
+        <v>59.35</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>22-02-2029</t>
+          <t>06-12-2028</t>
         </is>
       </c>
     </row>
@@ -1887,26 +1887,26 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>١٦</t>
+          <t>١٠</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>1077.76</v>
+        <v>702.4</v>
       </c>
       <c r="G40" t="n">
-        <v>62</v>
+        <v>29</v>
       </c>
       <c r="H40" t="n">
-        <v>56.13</v>
+        <v>58.53</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>67.36 جنيه</t>
+          <t>70.24 جنيه</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>12/2028</t>
+          <t>07/2028</t>
         </is>
       </c>
     </row>
@@ -1930,22 +1930,22 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="F41" t="n">
-        <v>12147.04</v>
+        <v>13447.92</v>
       </c>
       <c r="G41" t="n">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="H41" t="n">
-        <v>83.02</v>
+        <v>83.19</v>
       </c>
       <c r="I41" t="n">
-        <v>97.95999999999999</v>
+        <v>98.16</v>
       </c>
       <c r="J41" s="1" t="n">
-        <v>46892</v>
+        <v>46313</v>
       </c>
     </row>
     <row r="42">
@@ -1974,16 +1974,16 @@
         <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H42" t="n">
-        <v>61.7</v>
+        <v>63.05</v>
       </c>
       <c r="I42" t="n">
-        <v>73.42</v>
+        <v>75.03</v>
       </c>
       <c r="J42" s="1" t="n">
-        <v>46789</v>
+        <v>46937</v>
       </c>
     </row>
     <row r="43">
@@ -2006,22 +2006,22 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>107</v>
+        <v>161</v>
       </c>
       <c r="F43" t="n">
-        <v>6136.45</v>
+        <v>9315.459999999999</v>
       </c>
       <c r="G43" t="n">
-        <v>354</v>
+        <v>75</v>
       </c>
       <c r="H43" t="n">
-        <v>47.79</v>
+        <v>48.22</v>
       </c>
       <c r="I43" t="n">
-        <v>57.35</v>
+        <v>57.86</v>
       </c>
       <c r="J43" s="1" t="n">
-        <v>46317</v>
+        <v>47113</v>
       </c>
     </row>
     <row r="44">
@@ -2044,23 +2044,23 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="F44" t="n">
-        <v>4356.7</v>
+        <v>10404.28</v>
       </c>
       <c r="G44" t="n">
-        <v>51</v>
+        <v>73</v>
       </c>
       <c r="H44" t="n">
-        <v>399.7</v>
+        <v>415.01</v>
       </c>
       <c r="I44" t="n">
-        <v>435.67</v>
+        <v>452.36</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>02/2028</t>
+          <t>10/2027</t>
         </is>
       </c>
     </row>
@@ -2136,22 +2136,22 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F47" t="n">
-        <v>3105.22</v>
+        <v>3876.18</v>
       </c>
       <c r="G47" t="n">
-        <v>34</v>
+        <v>68</v>
       </c>
       <c r="H47" t="n">
-        <v>160.23</v>
+        <v>154.55</v>
       </c>
       <c r="I47" t="n">
-        <v>182.66</v>
+        <v>176.19</v>
       </c>
       <c r="J47" s="1" t="n">
-        <v>46534</v>
+        <v>46314</v>
       </c>
     </row>
     <row r="48">
@@ -2175,25 +2175,25 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>١١٦</t>
+          <t>٧٤</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>4,257.20 ج.م</t>
+          <t>2,682.50 ج.م</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>319</v>
+        <v>14</v>
       </c>
       <c r="H48" t="n">
-        <v>29.36</v>
+        <v>29</v>
       </c>
       <c r="I48" t="n">
-        <v>36.7</v>
+        <v>36.25</v>
       </c>
       <c r="J48" s="1" t="n">
-        <v>47143</v>
+        <v>46850</v>
       </c>
     </row>
     <row r="49">
@@ -2216,22 +2216,22 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F49" t="n">
-        <v>160.5</v>
+        <v>486.45</v>
       </c>
       <c r="G49" t="n">
-        <v>13</v>
+        <v>110</v>
       </c>
       <c r="H49" t="n">
-        <v>25.68</v>
+        <v>25.94</v>
       </c>
       <c r="I49" t="n">
-        <v>32.1</v>
+        <v>32.43</v>
       </c>
       <c r="J49" s="1" t="n">
-        <v>47108</v>
+        <v>46748</v>
       </c>
     </row>
     <row r="50">
@@ -2254,23 +2254,23 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="F50" t="n">
-        <v>4341.76</v>
+        <v>3895</v>
       </c>
       <c r="G50" t="n">
-        <v>309</v>
+        <v>32</v>
       </c>
       <c r="H50" t="n">
-        <v>33.3</v>
+        <v>33.33</v>
       </c>
       <c r="I50" t="n">
-        <v>40.96</v>
+        <v>41</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>05/2028</t>
+          <t>11/2026</t>
         </is>
       </c>
     </row>
@@ -2294,25 +2294,25 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>45</v>
+        <v>94</v>
       </c>
       <c r="F51" t="n">
-        <v>2155.95</v>
+        <v>4775.2</v>
       </c>
       <c r="G51" t="n">
-        <v>27</v>
+        <v>209</v>
       </c>
       <c r="H51" t="n">
-        <v>38.02</v>
+        <v>40.32</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>47.91 جنيه</t>
+          <t>50.8 جنيه</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>11-12-2026</t>
+          <t>22-11-2026</t>
         </is>
       </c>
     </row>
@@ -2336,19 +2336,19 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>524</v>
+        <v>371</v>
       </c>
       <c r="F52" t="n">
-        <v>143801.32</v>
+        <v>102581.5</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>232.57</v>
+        <v>234.32</v>
       </c>
       <c r="I52" t="n">
-        <v>274.43</v>
+        <v>276.5</v>
       </c>
     </row>
     <row r="53">
@@ -2377,16 +2377,16 @@
         <v>0</v>
       </c>
       <c r="G53" t="n">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="H53" t="n">
-        <v>47.48</v>
+        <v>46.57</v>
       </c>
       <c r="I53" t="n">
-        <v>58.88</v>
+        <v>57.75</v>
       </c>
       <c r="J53" s="1" t="n">
-        <v>46537</v>
+        <v>46815</v>
       </c>
     </row>
     <row r="54">
@@ -2410,24 +2410,24 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>٥٨</t>
+          <t>١٦٧</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>6351.58</v>
+        <v>19455.5</v>
       </c>
       <c r="G54" t="n">
-        <v>10</v>
+        <v>59</v>
       </c>
       <c r="H54" t="n">
-        <v>91.26000000000001</v>
+        <v>97.08</v>
       </c>
       <c r="I54" t="n">
-        <v>109.51</v>
+        <v>116.5</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>01/2028</t>
+          <t>11/2027</t>
         </is>
       </c>
     </row>
@@ -2459,16 +2459,16 @@
         </is>
       </c>
       <c r="G55" t="n">
-        <v>5</v>
+        <v>39</v>
       </c>
       <c r="H55" t="n">
-        <v>42.43</v>
+        <v>42.51</v>
       </c>
       <c r="I55" t="n">
-        <v>52.19</v>
+        <v>52.29</v>
       </c>
       <c r="J55" s="1" t="n">
-        <v>47070</v>
+        <v>46319</v>
       </c>
     </row>
     <row r="56">
@@ -2491,24 +2491,19 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>401</v>
+        <v>275</v>
       </c>
       <c r="F56" t="n">
-        <v>62572.04</v>
+        <v>45339.25</v>
       </c>
       <c r="G56" t="n">
-        <v>169</v>
+        <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>131.13</v>
+        <v>138.55</v>
       </c>
       <c r="I56" t="n">
-        <v>156.04</v>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>08-10-2028</t>
-        </is>
+        <v>164.87</v>
       </c>
     </row>
     <row r="57">
@@ -2531,19 +2526,19 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="F57" t="n">
-        <v>62888.64</v>
+        <v>60999.96</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>158.94</v>
+        <v>166.38</v>
       </c>
       <c r="I57" t="n">
-        <v>192.32</v>
+        <v>201.32</v>
       </c>
     </row>
     <row r="58">
@@ -2566,19 +2561,24 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>346</v>
+        <v>431</v>
       </c>
       <c r="F58" t="n">
-        <v>28455.04</v>
+        <v>34854.97</v>
       </c>
       <c r="G58" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H58" t="n">
-        <v>67.41</v>
+        <v>66.29000000000001</v>
       </c>
       <c r="I58" t="n">
-        <v>82.23999999999999</v>
+        <v>80.87</v>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>04/2028</t>
+        </is>
       </c>
     </row>
     <row r="59">
@@ -2601,22 +2601,22 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>39</v>
+        <v>143</v>
       </c>
       <c r="F59" t="n">
-        <v>2779.53</v>
+        <v>10446.15</v>
       </c>
       <c r="G59" t="n">
-        <v>2</v>
+        <v>102</v>
       </c>
       <c r="H59" t="n">
-        <v>58.9</v>
+        <v>60.37</v>
       </c>
       <c r="I59" t="n">
-        <v>71.27</v>
+        <v>73.05</v>
       </c>
       <c r="J59" s="1" t="n">
-        <v>46388</v>
+        <v>47215</v>
       </c>
     </row>
     <row r="60">
@@ -2640,25 +2640,25 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>٩</t>
+          <t>٢٥</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>257.94</v>
+        <v>681</v>
       </c>
       <c r="G60" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="H60" t="n">
-        <v>22.57</v>
+        <v>21.45</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>28.66 جنيه</t>
+          <t>27.24 جنيه</t>
         </is>
       </c>
       <c r="J60" s="1" t="n">
-        <v>46855</v>
+        <v>46320</v>
       </c>
     </row>
     <row r="61">
@@ -2681,23 +2681,23 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>285</v>
+        <v>214</v>
       </c>
       <c r="F61" t="n">
-        <v>11710.65</v>
+        <v>8936.639999999999</v>
       </c>
       <c r="G61" t="n">
-        <v>63</v>
+        <v>8</v>
       </c>
       <c r="H61" t="n">
-        <v>33.14</v>
+        <v>33.68</v>
       </c>
       <c r="I61" t="n">
-        <v>41.09</v>
+        <v>41.76</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>26-08-2027</t>
+          <t>29-07-2028</t>
         </is>
       </c>
     </row>
@@ -2721,25 +2721,25 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>14,096.70 ج.م</t>
+          <t>19,725.94 ج.م</t>
         </is>
       </c>
       <c r="G62" t="n">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="H62" t="n">
-        <v>663.6900000000001</v>
+        <v>642.96</v>
       </c>
       <c r="I62" t="n">
-        <v>783.15</v>
+        <v>758.6900000000001</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>12/2027</t>
+          <t>07/2027</t>
         </is>
       </c>
     </row>
@@ -2763,22 +2763,19 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>418</v>
+        <v>203</v>
       </c>
       <c r="F63" t="n">
-        <v>493302.7</v>
+        <v>238435.68</v>
       </c>
       <c r="G63" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>1017.37</v>
+        <v>1012.55</v>
       </c>
       <c r="I63" t="n">
-        <v>1180.15</v>
-      </c>
-      <c r="J63" s="1" t="n">
-        <v>46587</v>
+        <v>1174.56</v>
       </c>
     </row>
     <row r="64">
@@ -2807,16 +2804,16 @@
         <v>0</v>
       </c>
       <c r="G64" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="H64" t="n">
-        <v>536.8200000000001</v>
+        <v>564.9299999999999</v>
       </c>
       <c r="I64" t="n">
-        <v>628.08</v>
+        <v>660.97</v>
       </c>
       <c r="J64" s="1" t="n">
-        <v>46355</v>
+        <v>46801</v>
       </c>
     </row>
     <row r="65">
@@ -2839,22 +2836,22 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>102</v>
+        <v>39</v>
       </c>
       <c r="F65" t="n">
-        <v>87475.2</v>
+        <v>33001.8</v>
       </c>
       <c r="G65" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H65" t="n">
-        <v>732.99</v>
+        <v>723.25</v>
       </c>
       <c r="I65" t="n">
-        <v>857.6</v>
+        <v>846.2</v>
       </c>
       <c r="J65" s="1" t="n">
-        <v>46982</v>
+        <v>46727</v>
       </c>
     </row>
     <row r="66">
@@ -2878,20 +2875,20 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>٥</t>
+          <t>٢١</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>597.9</v>
+        <v>2307.9</v>
       </c>
       <c r="G66" t="n">
-        <v>4</v>
+        <v>45</v>
       </c>
       <c r="H66" t="n">
-        <v>99.65000000000001</v>
+        <v>91.58</v>
       </c>
       <c r="I66" t="n">
-        <v>119.58</v>
+        <v>109.9</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
@@ -2919,22 +2916,22 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>127</v>
+        <v>111</v>
       </c>
       <c r="F67" t="n">
-        <v>18869.66</v>
+        <v>15999.54</v>
       </c>
       <c r="G67" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="H67" t="n">
-        <v>124.86</v>
+        <v>121.13</v>
       </c>
       <c r="I67" t="n">
-        <v>148.58</v>
+        <v>144.14</v>
       </c>
       <c r="J67" s="1" t="n">
-        <v>47220</v>
+        <v>46347</v>
       </c>
     </row>
     <row r="68">
@@ -2957,22 +2954,22 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F68" t="n">
-        <v>42027.3</v>
+        <v>39288.96</v>
       </c>
       <c r="G68" t="n">
-        <v>38</v>
+        <v>321</v>
       </c>
       <c r="H68" t="n">
-        <v>400.79</v>
+        <v>421.92</v>
       </c>
       <c r="I68" t="n">
-        <v>428.85</v>
+        <v>409.26</v>
       </c>
       <c r="J68" s="1" t="n">
-        <v>46654</v>
+        <v>47056</v>
       </c>
     </row>
     <row r="69">
@@ -2995,26 +2992,26 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>1,208.58 ج.م</t>
+          <t>0.00 ج.م</t>
         </is>
       </c>
       <c r="G69" t="n">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="H69" t="n">
-        <v>207.66</v>
+        <v>222.07</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>201.43 جنيه</t>
+          <t>235.39 جنيه</t>
         </is>
       </c>
       <c r="J69" s="1" t="n">
-        <v>46551</v>
+        <v>46398</v>
       </c>
     </row>
     <row r="70">
@@ -3037,23 +3034,23 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F70" t="n">
-        <v>5616.8</v>
+        <v>4051.5</v>
       </c>
       <c r="G70" t="n">
-        <v>23</v>
+        <v>59</v>
       </c>
       <c r="H70" t="n">
-        <v>264.94</v>
+        <v>254.81</v>
       </c>
       <c r="I70" t="n">
-        <v>280.84</v>
+        <v>270.1</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>11/2028</t>
+          <t>06/2027</t>
         </is>
       </c>
     </row>
@@ -3077,23 +3074,23 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>235</v>
+        <v>187</v>
       </c>
       <c r="F71" t="n">
-        <v>41858.2</v>
+        <v>33549.67</v>
       </c>
       <c r="G71" t="n">
-        <v>103</v>
+        <v>6</v>
       </c>
       <c r="H71" t="n">
-        <v>148.43</v>
+        <v>149.51</v>
       </c>
       <c r="I71" t="n">
-        <v>178.12</v>
+        <v>179.41</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>26-08-2027</t>
+          <t>06-10-2026</t>
         </is>
       </c>
     </row>
@@ -3118,20 +3115,23 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>٤٩٣</t>
+          <t>٣٥٩</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>31034.35</v>
+        <v>22922.15</v>
       </c>
       <c r="G72" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="H72" t="n">
-        <v>51.18</v>
+        <v>51.91</v>
       </c>
       <c r="I72" t="n">
-        <v>62.95</v>
+        <v>63.85</v>
+      </c>
+      <c r="J72" s="1" t="n">
+        <v>46802</v>
       </c>
     </row>
     <row r="73">
@@ -3157,19 +3157,19 @@
         <v>138</v>
       </c>
       <c r="F73" t="n">
-        <v>4192.44</v>
+        <v>3851.58</v>
       </c>
       <c r="G73" t="n">
-        <v>41</v>
+        <v>91</v>
       </c>
       <c r="H73" t="n">
-        <v>24.11</v>
+        <v>22.15</v>
       </c>
       <c r="I73" t="n">
-        <v>30.38</v>
+        <v>27.91</v>
       </c>
       <c r="J73" s="1" t="n">
-        <v>47184</v>
+        <v>47111</v>
       </c>
     </row>
     <row r="74">
@@ -3192,23 +3192,23 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="F74" t="n">
-        <v>1838.1</v>
+        <v>2628.75</v>
       </c>
       <c r="G74" t="n">
-        <v>14</v>
+        <v>48</v>
       </c>
       <c r="H74" t="n">
-        <v>26.74</v>
+        <v>28.04</v>
       </c>
       <c r="I74" t="n">
-        <v>33.42</v>
+        <v>35.05</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>05/2028</t>
+          <t>12/2027</t>
         </is>
       </c>
     </row>
@@ -3238,16 +3238,16 @@
         <v>0</v>
       </c>
       <c r="G75" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="H75" t="n">
-        <v>20.88</v>
+        <v>20.81</v>
       </c>
       <c r="I75" t="n">
-        <v>26.31</v>
+        <v>26.22</v>
       </c>
       <c r="J75" s="1" t="n">
-        <v>46669</v>
+        <v>46791</v>
       </c>
     </row>
     <row r="76">
@@ -3270,25 +3270,25 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>60</v>
+        <v>129</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2,160.00 ج.م</t>
+          <t>4,545.96 ج.م</t>
         </is>
       </c>
       <c r="G76" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="H76" t="n">
-        <v>29.03</v>
+        <v>28.42</v>
       </c>
       <c r="I76" t="n">
-        <v>36</v>
+        <v>35.24</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>11-01-2027</t>
+          <t>21-12-2027</t>
         </is>
       </c>
     </row>
@@ -3318,16 +3318,16 @@
         <v>0</v>
       </c>
       <c r="G77" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H77" t="n">
-        <v>172.44</v>
+        <v>170.07</v>
       </c>
       <c r="I77" t="n">
-        <v>196.58</v>
+        <v>193.88</v>
       </c>
       <c r="J77" s="1" t="n">
-        <v>46370</v>
+        <v>47160</v>
       </c>
     </row>
     <row r="78">
@@ -3351,26 +3351,26 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>٢٢</t>
+          <t>٧</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>8862.48</v>
+        <v>2930.2</v>
       </c>
       <c r="G78" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="H78" t="n">
-        <v>350.3</v>
+        <v>364</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>402.84 جنيه</t>
+          <t>418.6 جنيه</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>10/2027</t>
+          <t>01/2028</t>
         </is>
       </c>
     </row>
@@ -3400,16 +3400,16 @@
         <v>0</v>
       </c>
       <c r="G79" t="n">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="H79" t="n">
-        <v>238</v>
+        <v>239.49</v>
       </c>
       <c r="I79" t="n">
-        <v>276.08</v>
+        <v>277.81</v>
       </c>
       <c r="J79" s="1" t="n">
-        <v>46798</v>
+        <v>47142</v>
       </c>
     </row>
     <row r="80">
@@ -3432,22 +3432,22 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>35</v>
+        <v>91</v>
       </c>
       <c r="F80" t="n">
-        <v>11796.05</v>
+        <v>32963.84</v>
       </c>
       <c r="G80" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="H80" t="n">
-        <v>300.92</v>
+        <v>323.43</v>
       </c>
       <c r="I80" t="n">
-        <v>337.03</v>
+        <v>362.24</v>
       </c>
       <c r="J80" s="1" t="n">
-        <v>46572</v>
+        <v>46781</v>
       </c>
     </row>
     <row r="81">
@@ -3470,23 +3470,23 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>150</v>
+        <v>161</v>
       </c>
       <c r="F81" t="n">
-        <v>11634</v>
+        <v>11897.9</v>
       </c>
       <c r="G81" t="n">
-        <v>106</v>
+        <v>8</v>
       </c>
       <c r="H81" t="n">
-        <v>64.63</v>
+        <v>61.58</v>
       </c>
       <c r="I81" t="n">
-        <v>77.56</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>29-10-2027</t>
+          <t>27-12-2026</t>
         </is>
       </c>
     </row>
@@ -3516,17 +3516,17 @@
         <v>0</v>
       </c>
       <c r="G82" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="H82" t="n">
-        <v>102.44</v>
+        <v>98.05</v>
       </c>
       <c r="I82" t="n">
-        <v>121.9</v>
+        <v>116.68</v>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>06/2028</t>
+          <t>07/2028</t>
         </is>
       </c>
     </row>
@@ -3558,16 +3558,16 @@
         </is>
       </c>
       <c r="G83" t="n">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="H83" t="n">
-        <v>370.63</v>
+        <v>386.84</v>
       </c>
       <c r="I83" t="n">
-        <v>415.11</v>
+        <v>433.26</v>
       </c>
       <c r="J83" s="1" t="n">
-        <v>46764</v>
+        <v>46341</v>
       </c>
     </row>
     <row r="84">
@@ -3591,23 +3591,23 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>١٥</t>
+          <t>٢١</t>
         </is>
       </c>
       <c r="F84" t="n">
-        <v>26125.8</v>
+        <v>37512.72</v>
       </c>
       <c r="G84" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="H84" t="n">
-        <v>1583.38</v>
+        <v>1623.93</v>
       </c>
       <c r="I84" t="n">
-        <v>1741.72</v>
+        <v>1786.32</v>
       </c>
       <c r="J84" s="1" t="n">
-        <v>47113</v>
+        <v>47085</v>
       </c>
     </row>
     <row r="85">
@@ -3639,13 +3639,13 @@
         <v>5</v>
       </c>
       <c r="H85" t="n">
-        <v>82.84999999999999</v>
+        <v>87.47</v>
       </c>
       <c r="I85" t="n">
-        <v>107.7</v>
+        <v>113.71</v>
       </c>
       <c r="J85" s="1" t="n">
-        <v>46996</v>
+        <v>46761</v>
       </c>
     </row>
     <row r="86">
@@ -3668,23 +3668,23 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F86" t="n">
-        <v>339.08</v>
+        <v>1161.15</v>
       </c>
       <c r="G86" t="n">
-        <v>7</v>
+        <v>118</v>
       </c>
       <c r="H86" t="n">
-        <v>62.79</v>
+        <v>57.34</v>
       </c>
       <c r="I86" t="n">
-        <v>84.77</v>
+        <v>77.41</v>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>09/2028</t>
+          <t>09/2026</t>
         </is>
       </c>
     </row>
@@ -3717,10 +3717,10 @@
         <v>0</v>
       </c>
       <c r="H87" t="n">
-        <v>79.09</v>
+        <v>73.56999999999999</v>
       </c>
       <c r="I87" t="n">
-        <v>91.73999999999999</v>
+        <v>85.34</v>
       </c>
     </row>
     <row r="88">
@@ -3768,13 +3768,13 @@
       </c>
       <c r="D90" t="inlineStr"/>
       <c r="E90" t="n">
-        <v>8479</v>
+        <v>6801</v>
       </c>
       <c r="F90" t="n">
-        <v>1826464.91</v>
+        <v>1377260.63</v>
       </c>
       <c r="G90" t="n">
-        <v>4475</v>
+        <v>3761</v>
       </c>
     </row>
   </sheetData>

--- a/sample_data/A_arabic_pharmacy_report.xlsx
+++ b/sample_data/A_arabic_pharmacy_report.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J90"/>
+  <dimension ref="A1:K90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -484,6 +484,11 @@
           <t>تاريخ الصلاحية</t>
         </is>
       </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>الشركة</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -522,6 +527,11 @@
       <c r="J5" s="1" t="n">
         <v>46567</v>
       </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>GSK Distribution</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -560,6 +570,11 @@
       <c r="J6" s="1" t="n">
         <v>47081</v>
       </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>GSK Distribution</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -598,6 +613,11 @@
       <c r="J7" s="1" t="n">
         <v>46849</v>
       </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>GSK Distribution</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -638,6 +658,11 @@
           <t>09/2027</t>
         </is>
       </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>GSK Distribution</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -678,6 +703,11 @@
           <t>28-10-2028</t>
         </is>
       </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>GSK Distribution</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -718,6 +748,11 @@
       <c r="J10" s="1" t="n">
         <v>46925</v>
       </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>GSK Distribution</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -758,6 +793,11 @@
       <c r="J11" s="1" t="n">
         <v>46677</v>
       </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>GSK Distribution</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -798,6 +838,11 @@
           <t>08/2028</t>
         </is>
       </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>GSK Distribution</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -838,6 +883,11 @@
       <c r="J13" s="1" t="n">
         <v>46767</v>
       </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>GSK Distribution</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -878,6 +928,11 @@
           <t>22-03-2028</t>
         </is>
       </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>GSK Distribution</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -916,6 +971,11 @@
       <c r="J15" s="1" t="n">
         <v>46371</v>
       </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>GSK Distribution</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -958,6 +1018,11 @@
           <t>04/2028</t>
         </is>
       </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>GSK Distribution</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -996,6 +1061,11 @@
       <c r="J17" s="1" t="n">
         <v>46548</v>
       </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>GSK Distribution</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1036,6 +1106,11 @@
       <c r="J18" s="1" t="n">
         <v>46849</v>
       </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Pharma Overseas</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1076,6 +1151,11 @@
           <t>29-11-2026</t>
         </is>
       </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Pharma Overseas</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1116,6 +1196,11 @@
           <t>03/2029</t>
         </is>
       </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Pharma Overseas</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1154,6 +1239,11 @@
       <c r="J21" s="1" t="n">
         <v>47219</v>
       </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Pharma Overseas</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1196,6 +1286,11 @@
       <c r="J22" s="1" t="n">
         <v>46982</v>
       </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Pharma Overseas</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1234,6 +1329,11 @@
       <c r="J23" s="1" t="n">
         <v>46706</v>
       </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Pharma Overseas</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1274,6 +1374,11 @@
           <t>04/2028</t>
         </is>
       </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Pharma Overseas</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1314,6 +1419,11 @@
       <c r="J25" s="1" t="n">
         <v>46542</v>
       </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Pharma Overseas</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1349,6 +1459,11 @@
       <c r="I26" t="n">
         <v>68.45</v>
       </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Pharma Overseas</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1387,6 +1502,11 @@
       <c r="J27" s="1" t="n">
         <v>47047</v>
       </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Pharma Overseas</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1429,6 +1549,11 @@
           <t>04/2028</t>
         </is>
       </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Pharma Overseas</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1469,6 +1594,11 @@
           <t>23-01-2029</t>
         </is>
       </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Pharma Overseas</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1507,6 +1637,11 @@
       <c r="J30" s="1" t="n">
         <v>46796</v>
       </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Pharma Overseas</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1547,6 +1682,11 @@
       <c r="J31" s="1" t="n">
         <v>46965</v>
       </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Pharma Overseas</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1589,6 +1729,11 @@
           <t>05/2028</t>
         </is>
       </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Ibnsina Pharma</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1627,6 +1772,11 @@
       <c r="J33" s="1" t="n">
         <v>46997</v>
       </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Ibnsina Pharma</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1669,6 +1819,11 @@
           <t>20-03-2028</t>
         </is>
       </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Ibnsina Pharma</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1707,6 +1862,11 @@
       <c r="J35" s="1" t="n">
         <v>47008</v>
       </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Ibnsina Pharma</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1747,6 +1907,11 @@
           <t>12/2028</t>
         </is>
       </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Ibnsina Pharma</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1785,6 +1950,11 @@
       <c r="J37" s="1" t="n">
         <v>46875</v>
       </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Ibnsina Pharma</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -1823,6 +1993,11 @@
       <c r="J38" s="1" t="n">
         <v>46929</v>
       </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Ibnsina Pharma</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -1865,6 +2040,11 @@
           <t>06-12-2028</t>
         </is>
       </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>GSK Distribution</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -1909,6 +2089,11 @@
           <t>07/2028</t>
         </is>
       </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>GSK Distribution</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -1947,6 +2132,11 @@
       <c r="J41" s="1" t="n">
         <v>46313</v>
       </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>GSK Distribution</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -1985,6 +2175,11 @@
       <c r="J42" s="1" t="n">
         <v>46937</v>
       </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>GSK Distribution</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -2023,6 +2218,11 @@
       <c r="J43" s="1" t="n">
         <v>47113</v>
       </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Ibnsina Pharma</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -2063,6 +2263,11 @@
           <t>10/2027</t>
         </is>
       </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Ibnsina Pharma</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2113,6 +2318,11 @@
       <c r="J46" t="inlineStr">
         <is>
           <t>تاريخ الصلاحية</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>الشركة</t>
         </is>
       </c>
     </row>
@@ -2153,6 +2363,11 @@
       <c r="J47" s="1" t="n">
         <v>46314</v>
       </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Ibnsina Pharma</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -2195,6 +2410,11 @@
       <c r="J48" s="1" t="n">
         <v>46850</v>
       </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Ibnsina Pharma</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -2233,6 +2453,11 @@
       <c r="J49" s="1" t="n">
         <v>46748</v>
       </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Ibnsina Pharma</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -2273,6 +2498,11 @@
           <t>11/2026</t>
         </is>
       </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Ibnsina Pharma</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -2315,6 +2545,11 @@
           <t>22-11-2026</t>
         </is>
       </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>United Company</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -2350,6 +2585,11 @@
       <c r="I52" t="n">
         <v>276.5</v>
       </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>United Company</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -2388,6 +2628,11 @@
       <c r="J53" s="1" t="n">
         <v>46815</v>
       </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>United Company</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -2430,6 +2675,11 @@
           <t>11/2027</t>
         </is>
       </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>United Company</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -2470,6 +2720,11 @@
       <c r="J55" s="1" t="n">
         <v>46319</v>
       </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>United Company</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -2505,6 +2760,11 @@
       <c r="I56" t="n">
         <v>164.87</v>
       </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>United Company</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -2540,6 +2800,11 @@
       <c r="I57" t="n">
         <v>201.32</v>
       </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>United Company</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -2580,6 +2845,11 @@
           <t>04/2028</t>
         </is>
       </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>United Company</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -2618,6 +2888,11 @@
       <c r="J59" s="1" t="n">
         <v>47215</v>
       </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>United Company</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -2660,6 +2935,11 @@
       <c r="J60" s="1" t="n">
         <v>46320</v>
       </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>United Company</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -2700,6 +2980,11 @@
           <t>29-07-2028</t>
         </is>
       </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>United Company</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -2742,6 +3027,11 @@
           <t>07/2027</t>
         </is>
       </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Beauty Hub</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -2777,6 +3067,11 @@
       <c r="I63" t="n">
         <v>1174.56</v>
       </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Beauty Hub</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -2815,6 +3110,11 @@
       <c r="J64" s="1" t="n">
         <v>46801</v>
       </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Beauty Hub</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -2853,6 +3153,11 @@
       <c r="J65" s="1" t="n">
         <v>46727</v>
       </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Beauty Hub</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -2895,6 +3200,11 @@
           <t>02/2028</t>
         </is>
       </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>United Company</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -2933,6 +3243,11 @@
       <c r="J67" s="1" t="n">
         <v>46347</v>
       </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>United Company</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -2971,6 +3286,11 @@
       <c r="J68" s="1" t="n">
         <v>47056</v>
       </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Mother &amp; Baby Co</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -3013,6 +3333,11 @@
       <c r="J69" s="1" t="n">
         <v>46398</v>
       </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Mother &amp; Baby Co</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -3053,6 +3378,11 @@
           <t>06/2027</t>
         </is>
       </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Mother &amp; Baby Co</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -3093,6 +3423,11 @@
           <t>06-10-2026</t>
         </is>
       </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Mother &amp; Baby Co</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -3133,6 +3468,11 @@
       <c r="J72" s="1" t="n">
         <v>46802</v>
       </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Ibnsina Pharma</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -3171,6 +3511,11 @@
       <c r="J73" s="1" t="n">
         <v>47111</v>
       </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Ibnsina Pharma</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -3211,6 +3556,11 @@
           <t>12/2027</t>
         </is>
       </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Ibnsina Pharma</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -3249,6 +3599,11 @@
       <c r="J75" s="1" t="n">
         <v>46791</v>
       </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Ibnsina Pharma</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -3291,6 +3646,11 @@
           <t>21-12-2027</t>
         </is>
       </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Pharma Overseas</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -3329,6 +3689,11 @@
       <c r="J77" s="1" t="n">
         <v>47160</v>
       </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Pharma Overseas</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -3373,6 +3738,11 @@
           <t>01/2028</t>
         </is>
       </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Pharma Overseas</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -3411,6 +3781,11 @@
       <c r="J79" s="1" t="n">
         <v>47142</v>
       </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Pharma Overseas</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -3449,6 +3824,11 @@
       <c r="J80" s="1" t="n">
         <v>46781</v>
       </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Ibnsina Pharma</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -3489,6 +3869,11 @@
           <t>27-12-2026</t>
         </is>
       </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Ibnsina Pharma</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -3529,6 +3914,11 @@
           <t>07/2028</t>
         </is>
       </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Ibnsina Pharma</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -3569,6 +3959,11 @@
       <c r="J83" s="1" t="n">
         <v>46341</v>
       </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>MedTech Supplies</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -3609,6 +4004,11 @@
       <c r="J84" s="1" t="n">
         <v>47085</v>
       </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>MedTech Supplies</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -3647,6 +4047,11 @@
       <c r="J85" s="1" t="n">
         <v>46761</v>
       </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>MedTech Supplies</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -3685,6 +4090,11 @@
       <c r="J86" t="inlineStr">
         <is>
           <t>09/2026</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>MedTech Supplies</t>
         </is>
       </c>
     </row>
